--- a/output/FN/FN.xlsx
+++ b/output/FN/FN.xlsx
@@ -29,7 +29,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -83,12 +83,6 @@
       <name val="Consolas"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00991B1B"/>
-      <sz val="10"/>
-    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -140,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -171,7 +165,6 @@
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -581,7 +574,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>$251</t>
+          <t>$234</t>
         </is>
       </c>
     </row>
@@ -603,7 +596,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>-57.2%</t>
+          <t>-60.1%</t>
         </is>
       </c>
     </row>
@@ -615,7 +608,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>$251</t>
+          <t>$234</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -625,7 +618,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>-57.2%</t>
+          <t>-60.1%</t>
         </is>
       </c>
     </row>
@@ -1001,7 +994,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Bear 25% because customer concentration, thin margins and a ~2.5x run leave little room for error, and co-packaged optics is a structural overhang. Base 45% for the continued AI optical ramp. Bull 15% for a CPO/1.6T assembly win. Cross-check 20% anchors against optical/manufacturing multiples.</t>
+          <t>Bear 25% because customer concentration, thin margins and a ~2.5x run leave little room for error, and co-packaged optics is a structural overhang. Base 45% for the continued AI optical ramp. Bull 10% for a CPO/1.6T assembly win. Cross-check 20% anchors against optical/manufacturing multiples.</t>
         </is>
       </c>
     </row>
@@ -3662,10 +3655,10 @@
         <v>338.32</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="D7" t="n">
-        <v>50.75</v>
+        <v>33.83</v>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
@@ -3711,13 +3704,8 @@
           <t>Weight total</t>
         </is>
       </c>
-      <c r="C10" s="25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="E10" s="26" t="inlineStr">
-        <is>
-          <t>WARNING: weights do not sum to 1.0</t>
-        </is>
+      <c r="C10" s="11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -3727,7 +3715,7 @@
         </is>
       </c>
       <c r="D11" s="19" t="n">
-        <v>250.61</v>
+        <v>233.69</v>
       </c>
     </row>
     <row r="12">
@@ -3747,7 +3735,7 @@
         </is>
       </c>
       <c r="D13" s="25" t="n">
-        <v>-0.5720000000000001</v>
+        <v>-0.601</v>
       </c>
     </row>
     <row r="14"/>
@@ -3762,7 +3750,7 @@
     <row r="17" ht="60" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Bear 25% because customer concentration, thin margins and a ~2.5x run leave little room for error, and co-packaged optics is a structural overhang. Base 45% for the continued AI optical ramp. Bull 15% for a CPO/1.6T assembly win. Cross-check 20% anchors against optical/manufacturing multiples.</t>
+          <t>Bear 25% because customer concentration, thin margins and a ~2.5x run leave little room for error, and co-packaged optics is a structural overhang. Base 45% for the continued AI optical ramp. Bull 10% for a CPO/1.6T assembly win. Cross-check 20% anchors against optical/manufacturing multiples.</t>
         </is>
       </c>
     </row>

--- a/output/FN/FN.xlsx
+++ b/output/FN/FN.xlsx
@@ -551,7 +551,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Institutional Equity Research  |  Date: 2026-06-10  |  Listings: NYSE  |  Engine: himself65/finance-skills</t>
+          <t>Institutional Equity Research  |  Date: 2026-06-17  |  Listings: NYSE  |  Engine: himself65/finance-skills</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>$234</t>
+          <t>$282</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>$586</t>
+          <t>$587</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>-60.1%</t>
+          <t>-51.9%</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>$234</t>
+          <t>$282</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>-60.1%</t>
+          <t>-51.9%</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>~$20.1B</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>~$3.4B</t>
+          <t>~$3.43B (+19% YoY)</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>34.1x</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>~5x</t>
+          <t>42.0x</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>~1.3</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>10.80%</t>
+          <t>10.50%</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>10.80%</t>
+          <t>10.48%</t>
         </is>
       </c>
     </row>
@@ -806,7 +806,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>$245</t>
+          <t>$262</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>$268</t>
+          <t>$338</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Fabrinet is the trusted contract manufacturer behind the industry's most complex optical modules, assembling the 800G and 1.6T transceivers and silicon-photonics engines that the leading optical and networking vendors design but do not build themselves.</t>
+          <t>Fabrinet is the world's only scaled precision optical assembler capable of building 800G and 1.6T transceivers, DCI coherent modules, and high-performance compute assemblies at the volumes the leading OEMs require -- a position cemented by 20+ years of tooling, process know-how, and a Thai manufacturing base that no competitor has replicated.</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Its precision optical-packaging expertise, scaled Thai manufacturing base and long relationships with the top transceiver and networking customers make it the default high-complexity optical assembler, riding the same AI-interconnect wave as the component makers.</t>
+          <t>DCI revenue grew 90% year-over-year to $197M in Q3 FY2026, supply constraints depressed Datacom by $150-200M versus actual demand, and the HPC ramp targets $150M+ quarterly -- three simultaneous inflections mean FY2027 FCF will be materially higher than today's negative trailing-twelve-month figure once Building 10 CapEx is absorbed.</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>But Fabrinet earns a ~12-13% operating margin as an assembler and now trades near 6x sales. Even a DCF that extrapolates the AI-optical ramp lands near $245 against a $586 stock. A great operator, priced like the chip designers it serves.</t>
+          <t>At 42x trailing EBITDA and 9x book value with negative trailing FCF and 0.24% insider ownership, the stock prices in a decade of frictionless growth for a 12% gross-margin contract assembler; the base-case DCF at 10.5% WACC returns $262, the blended target is $282, and the stock needs to fall 52% before the math works.</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>DCF — Fabrinet generates steady, positive free cash flow as the contract assembler behind the leading AI optical-module programs, so an FCFF DCF is appropriate. Because it is a thin-margin assembler trading at a rich post-run multiple, an EV/EBITDA cross-check against optical and manufacturing peers disciplines the target.</t>
+          <t>DCF — Fabrinet generates positive, growing free cash flow from optical and electronic contract assembly. The FCF yield is temporarily depressed by Building 10 construction CapEx ($130-132M total, mostly FY2026); the normalized FCF power is materially higher from FY2027 onward. FCFF DCF is the correct primary method. An EV/EBITDA cross-check against optical-component and EMS peers disciplines the terminal implied price.</t>
         </is>
       </c>
     </row>
@@ -955,7 +955,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Ke = 4.3% Rf + 1.30 beta x 5.0% ERP = 10.8%. Net-cash balance sheet sets WACC = Ke at 10.8%. Beta reflects customer concentration and datacom cyclicality offset by a debt-free balance sheet.</t>
+          <t>Ke = 4.5% Rf + 1.30 beta x 4.6% ERP = 10.5%. Net-cash balance sheet (total debt $4.4M vs $945M cash) means WACC tracks Ke closely. Beta 1.3 reflects customer concentration (implied top-2 customers ~35-40% of revenue), thin gross margins (12%), and Thailand single-country manufacturing risk. Offset partially by debt-free structure and proven long-term execution. 10.5% sits at the top of the ems sector band (8.0-10.5%).</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>3.0% terminal: optical assembly is a GDP-plus business once the AI build matures; thin margins and customer concentration cap the durable growth rate.</t>
+          <t>3.0% terminal: secular AI optical demand plus CPO/OCS optionality supports above-GDP terminal growth. Capped at 3.0% because contract assemblers without product IP cannot sustainably grow faster than nominal GDP plus the tech intensity premium without capturing more of the value chain.</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Multiple — EV/EBITDA cross-check against optical-component and contract-manufacturing peers. Even a generous multiple for an asset-light optical assembler lands below the post-run share price.</t>
+          <t>Multiple — EV/EBITDA cross-check blending optical-component peers (COHR ~35-40x, LITE ~22x) with EMS peers (SANM ~9x, FLEX ~9x, CLS ~15x). Fabrinet earns a premium over generic EMS for optical complexity and secular growth, but trades at a discount to optical-IP companies. A blended cross-check multiple of 20x applied to FY2026E EBITDA is defensible at the midpoint.</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Bear 25% because customer concentration, thin margins and a ~2.5x run leave little room for error, and co-packaged optics is a structural overhang. Base 45% for the continued AI optical ramp. Bull 10% for a CPO/1.6T assembly win. Cross-check 20% anchors against optical/manufacturing multiples.</t>
+          <t>Base 50% is the anchor: modeled revenue growth and margin expansion are realistic given actual Q3 FY2026 results, but the DCF says fair value is well below spot. Bear 20% acknowledges the real risk that Datacom demand is inventory-cycle driven rather than structural, and that any customer concentration event can step revenues down sharply. Bull 15% reflects the genuine optionality in CPO/OCS/hyperscale Datacom wins that are being actively qualified. Cross-check 15% adds a relative discipline: even at a generous 20x EBITDA versus EMS peers at 9-15x, the stock is rich. Probabilities sum with cross-check: 0.20 + 0.50 + 0.15 + 0.15 = 1.00.</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>yfinance fundamentals were thin this session; revenue (~$3.4B), net cash (~$0.9B) and margins are from general disclosure. | Per-customer concentration is undisclosed at line-item level; optical-OEM exposure is inferred from industry reporting. | Forward EBITDA (~$0.58B) used in the cross-check is an estimate. | Short interest and positioning feeds were not retrievable this session.</t>
+          <t>YTD return not retrieved -- would require Jan 1 2026 price from a price history endpoint. | Analyst consensus PT (mean/median) not retrieved -- Bloomberg or Reuters consensus not available via current tools. | Short interest detail beyond 8.1% float percentage not retrieved. | Per-customer revenue concentration not disclosed below the 10% threshold in FN 10-K filings; Nvidia, AWS, and coherent OEM exposure estimated from transcript language. | FY2025 full year revenue is derived from CEO statement of 19% YoY growth over FY2024 $2.883B ($3.43B); direct 10-K filing not read this session. | FY2025 EBITDA and FCF are estimates based on margin rates from Q4 FY2025 annual income statement data; segment-level margins not disclosed. | ADTV and 30-day realized volatility not retrieved. | Insider transaction dates and dollar values not retrieved from yfinance for recent filings.</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>$586.00</t>
+          <t>$587.41</t>
         </is>
       </c>
     </row>
@@ -1083,19 +1083,19 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>$236.86 to $748.89</t>
+          <t>$258.10 to $748.89</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Drawdown from high</t>
+          <t>Drawdown from 52w high</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>-21.8%</t>
+          <t>-21.5%</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>+140% (approx)</t>
+          <t>~+128% (from 52w low $258)</t>
         </is>
       </c>
     </row>
@@ -1126,24 +1126,24 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Shares out</t>
+          <t>Enterprise value</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>35.8M</t>
+          <t>~$20.1B</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Net cash (est)</t>
+          <t>Net cash</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>~$0.9B</t>
+          <t>+$941M (total cash $945M, total debt $4M)</t>
         </is>
       </c>
     </row>
@@ -1155,67 +1155,175 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>~$3.4B</t>
+          <t>~$3.43B (+19% YoY)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>EV/Sales (fwd, est)</t>
+          <t>FY25 EBITDA / margin (est)</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>~5x</t>
+          <t>~$395M / 11.5%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Operating margin (est)</t>
+          <t>FY25 FCF (est)</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>~12.5%</t>
+          <t>~$200M (CapEx elevated vs norm)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Primary method</t>
+          <t>TTM revenue</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>DCF (FCFF)</t>
+          <t>$4.24B</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Cross-check</t>
+          <t>TTM EBITDA</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>EV/EBITDA 15x</t>
+          <t>$480M</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Intrinsic vs price</t>
+          <t>TTM FCF</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>-57%</t>
+          <t>-$79M (Building 10 CapEx peak)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>FY26E non-GAAP EPS (run rate)</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>~$14-15 (Q3 $3.72 x 4 adj)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Forward P/E (Street est)</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>34.1x</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>EV / EBITDA (TTM)</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>42.0x</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Price / Book</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>9.1x (book value $64/share)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Gross margin (TTM)</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>12.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Operating margin (TTM)</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>9.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>~1.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Insider ownership</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>0.24%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Dividend yield</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1234,9 +1342,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -1288,10 +1396,10 @@
         <v>2.65</v>
       </c>
       <c r="D4" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="5">
@@ -1300,19 +1408,17 @@
           <t>Revenue growth YoY</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+      <c r="B5" s="11" t="n">
+        <v>0.204</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>0.173</v>
+        <v>0.169</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>0.106</v>
+        <v>0.09</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="6">
@@ -1322,16 +1428,16 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="D6" s="11" t="n">
         <v>0.124</v>
       </c>
-      <c r="C6" s="11" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>0.126</v>
-      </c>
       <c r="E6" s="11" t="n">
-        <v>0.128</v>
+        <v>0.121</v>
       </c>
     </row>
     <row r="7">
@@ -1341,16 +1447,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>290</v>
+        <v>249</v>
       </c>
       <c r="C7" t="n">
-        <v>345</v>
+        <v>304</v>
       </c>
       <c r="D7" t="n">
-        <v>390</v>
+        <v>334</v>
       </c>
       <c r="E7" t="n">
-        <v>460</v>
+        <v>395</v>
       </c>
     </row>
     <row r="8">
@@ -1360,16 +1466,16 @@
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>0.128</v>
+        <v>0.11</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>0.13</v>
+        <v>0.115</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>0.133</v>
+        <v>0.116</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>0.135</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="9">
@@ -1379,16 +1485,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>248</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="E9" t="n">
-        <v>360</v>
+        <v>348</v>
       </c>
     </row>
     <row r="10">
@@ -1398,16 +1504,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="E10" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11">
@@ -1417,16 +1523,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.9</v>
+        <v>5.43</v>
       </c>
       <c r="C11" t="n">
-        <v>7.2</v>
+        <v>6.79</v>
       </c>
       <c r="D11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.17</v>
       </c>
       <c r="E11" t="n">
-        <v>9.9</v>
+        <v>9.23</v>
       </c>
     </row>
   </sheetData>
@@ -1493,7 +1599,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0.108</v>
+        <v>0.105</v>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
@@ -1502,7 +1608,7 @@
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Ke = 4.3% Rf + 1.30 beta x 5.0% ERP = 10.8%. Net-cash balance sheet sets WACC = Ke at 10.8%. Beta reflects customer concentration and datacom cyclicality offset by a debt-free balance sheet.</t>
+          <t>Ke = 4.5% Rf + 1.30 beta x 4.6% ERP = 10.5%. Net-cash balance sheet (total debt $4.4M vs $945M cash) means WACC tracks Ke closely. Beta 1.3 reflects customer concentration (implied top-2 customers ~35-40% of revenue), thin gross margins (12%), and Thailand single-country manufacturing risk. Offset partially by debt-free structure and proven long-term execution. 10.5% sits at the top of the ems sector band (8.0-10.5%).</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1619,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.043</v>
+        <v>0.045</v>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
@@ -1553,7 +1659,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>0.05</v>
+        <v>0.046</v>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
@@ -1573,7 +1679,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
@@ -1593,7 +1699,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
@@ -1622,7 +1728,7 @@
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>3.0% terminal: optical assembly is a GDP-plus business once the AI build matures; thin margins and customer concentration cap the durable growth rate.</t>
+          <t>3.0% terminal: secular AI optical demand plus CPO/OCS optionality supports above-GDP terminal growth. Capped at 3.0% because contract assemblers without product IP cannot sustainably grow faster than nominal GDP plus the tech intensity premium without capturing more of the value chain.</t>
         </is>
       </c>
     </row>
@@ -1677,14 +1783,14 @@
         <v>2026</v>
       </c>
       <c r="B16" t="n">
-        <v>0.315</v>
+        <v>0.233</v>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>4.65</v>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>FY26E (Jun) +18%: datacom optical-module assembly for AI (800G/1.6T) drives the ramp; Fabrinet is the contract manufacturer behind the leading transceiver and silicon-photonics programs.</t>
+          <t>FY2026 (ends Aug 2026): Q1-Q3 actual + Q4 guide midpoint $1.27B = $4.65B total. +35.6% YoY. CapEx elevated at 5.2% of revenue ($241M) due to Building 10 construction ($130-132M total). GAAP EBIT margin ~10.0% consistent with Q3 FY2026 non-GAAP OM of 10.7% adjusted for stock comp. Tax rate 8% per CFO guidance of mid-single-digit effective GAAP rate for FY2026. Low tax reflects Thailand manufacturing structure.</t>
         </is>
       </c>
     </row>
@@ -1693,14 +1799,14 @@
         <v>2027</v>
       </c>
       <c r="B17" t="n">
-        <v>0.387</v>
+        <v>0.462</v>
       </c>
       <c r="C17" t="n">
-        <v>4.66</v>
+        <v>5.5</v>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>+16.5%: 1.6T volume scales and new optical-engine programs onshore; modest margin lift from mix and scale.</t>
+          <t>+18.3%: Building 10 commissions (Jan 2027 opening ceremony), adding $3B capacity. Datacom supply constraints ease as laser and memory supply catches up; pent-up demand releases. New hyperscale Datacom (2 programs) and merchant vendor programs ramp from early qualification to volume. HPC program reaches fully-ramped $150M+/quarter run rate. CapEx normalizes to 2.5% (maintenance + Navanakorn fit-out).</t>
         </is>
       </c>
     </row>
@@ -1709,14 +1815,14 @@
         <v>2028</v>
       </c>
       <c r="B18" t="n">
-        <v>0.475</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="C18" t="n">
-        <v>5.31</v>
+        <v>6.1</v>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>+14%: AI optical content keeps compounding; margins inch up on automation.</t>
+          <t>+10.9%: 1.6T transceiver ramp in full production; DCI moves to 800G ZR volume; HPC second-phase programs. Margin improves to 11.0% as new programs mature past ramp-inefficiency phase. CapEx 2.0% is maintenance-level plus early Building 11 site work.</t>
         </is>
       </c>
     </row>
@@ -1725,14 +1831,14 @@
         <v>2029</v>
       </c>
       <c r="B19" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.652</v>
       </c>
       <c r="C19" t="n">
-        <v>5.95</v>
+        <v>6.65</v>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>+12%: growth normalizes; FN remains a key Western/Thai assembly node.</t>
+          <t>+9.0%: steady growth as AI interconnect demand remains elevated; CPO assembly volume begins contributing from Raytek-partnership programs. Growth decelerates as the AI-optical ramp matures off a large base.</t>
         </is>
       </c>
     </row>
@@ -1741,14 +1847,14 @@
         <v>2030</v>
       </c>
       <c r="B20" t="n">
-        <v>0.651</v>
+        <v>0.729</v>
       </c>
       <c r="C20" t="n">
-        <v>6.55</v>
+        <v>7.15</v>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>+10%: steady compounding on a larger base.</t>
+          <t>+7.5%: maturing optical-interconnect cycle; OCS and CPO add incremental revenue streams. Operating margin approaching 11.5% as a larger portion of work is on high-complexity, premium-margin programs.</t>
         </is>
       </c>
     </row>
@@ -1757,14 +1863,14 @@
         <v>2031</v>
       </c>
       <c r="B21" t="n">
-        <v>0.728</v>
+        <v>0.781</v>
       </c>
       <c r="C21" t="n">
-        <v>7.07</v>
+        <v>7.58</v>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>+8%: deceleration continues.</t>
+          <t>+6.0%: optical assembly volume grows in line with data center bandwidth demands; growth rate continues toward long-run steady state.</t>
         </is>
       </c>
     </row>
@@ -1773,14 +1879,14 @@
         <v>2032</v>
       </c>
       <c r="B22" t="n">
-        <v>0.793</v>
+        <v>0.82</v>
       </c>
       <c r="C22" t="n">
-        <v>7.57</v>
+        <v>7.96</v>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>+7%: maturing growth.</t>
+          <t>+5.0%: approaching terminal growth rate; sustained by replacement cycles, bandwidth upgrades, and global data center expansion outside North America.</t>
         </is>
       </c>
     </row>
@@ -1792,11 +1898,11 @@
         <v>0.861</v>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>+5.7%: approaching steady state, ~14% operating margin franchise.</t>
+          <t>+4.0%: one year above terminal growth, reflecting the optical assembly market still in secular expansion driven by global bandwidth demand; bridges to terminal.</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1979,7 @@
         </is>
       </c>
       <c r="C5" s="13" t="n">
-        <v>0.043</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="6">
@@ -1903,7 +2009,7 @@
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>0.05</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="8">
@@ -1918,7 +2024,7 @@
         </is>
       </c>
       <c r="C8" s="13" t="n">
-        <v>0.108</v>
+        <v>0.1048</v>
       </c>
     </row>
     <row r="9">
@@ -1933,7 +2039,7 @@
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="10">
@@ -1948,7 +2054,7 @@
         </is>
       </c>
       <c r="C10" s="13" t="n">
-        <v>1</v>
+        <v>0.998</v>
       </c>
     </row>
     <row r="11">
@@ -1963,7 +2069,7 @@
         </is>
       </c>
       <c r="C11" s="13" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="12">
@@ -1978,7 +2084,7 @@
         </is>
       </c>
       <c r="C12" s="13" t="n">
-        <v>0.108</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="13"/>
@@ -2009,7 +2115,7 @@
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>10.80% — within band (8.0%-12.0%)</t>
+          <t>10.50% — within band (8.0%-12.0%)</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2127,7 @@
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>10.8% equals Ke on net cash; mid-band for a concentrated, thin-margin assembler.</t>
+          <t>10.5% is at the ceiling of the EMS sector band. Justified by customer-concentration, geographic-concentration (Thailand), and the premium multiple investors currently assign, which creates higher required return to validate ownership.</t>
         </is>
       </c>
     </row>
@@ -2087,28 +2193,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>4.65</v>
       </c>
       <c r="C21" t="n">
-        <v>4.66</v>
+        <v>5.5</v>
       </c>
       <c r="D21" t="n">
-        <v>5.31</v>
+        <v>6.1</v>
       </c>
       <c r="E21" t="n">
-        <v>5.95</v>
+        <v>6.65</v>
       </c>
       <c r="F21" t="n">
-        <v>6.55</v>
+        <v>7.15</v>
       </c>
       <c r="G21" t="n">
-        <v>7.07</v>
+        <v>7.58</v>
       </c>
       <c r="H21" t="n">
-        <v>7.57</v>
+        <v>7.96</v>
       </c>
       <c r="I21" t="n">
-        <v>8</v>
+        <v>8.279999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -2118,28 +2224,28 @@
         </is>
       </c>
       <c r="B22" s="11" t="n">
-        <v>0.18</v>
+        <v>0.356</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>0.165</v>
+        <v>0.183</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>0.14</v>
+        <v>0.109</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.1</v>
+        <v>0.075</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H22" s="11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>0.057</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="23">
@@ -2149,28 +2255,28 @@
         </is>
       </c>
       <c r="B23" s="11" t="n">
-        <v>0.125</v>
+        <v>0.1</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>0.128</v>
+        <v>0.108</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>0.131</v>
+        <v>0.11</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.134</v>
+        <v>0.112</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.136</v>
+        <v>0.115</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.138</v>
+        <v>0.115</v>
       </c>
       <c r="H23" s="11" t="n">
-        <v>0.139</v>
+        <v>0.115</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>0.14</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="24">
@@ -2180,28 +2286,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5</v>
+        <v>0.465</v>
       </c>
       <c r="C24" t="n">
-        <v>0.596</v>
+        <v>0.594</v>
       </c>
       <c r="D24" t="n">
-        <v>0.696</v>
+        <v>0.671</v>
       </c>
       <c r="E24" t="n">
-        <v>0.797</v>
+        <v>0.745</v>
       </c>
       <c r="F24" t="n">
-        <v>0.891</v>
+        <v>0.822</v>
       </c>
       <c r="G24" t="n">
-        <v>0.976</v>
+        <v>0.872</v>
       </c>
       <c r="H24" t="n">
-        <v>1.052</v>
+        <v>0.915</v>
       </c>
       <c r="I24" t="n">
-        <v>1.12</v>
+        <v>0.952</v>
       </c>
     </row>
     <row r="25">
@@ -2211,28 +2317,28 @@
         </is>
       </c>
       <c r="B25" s="11" t="n">
-        <v>0.21</v>
+        <v>0.08</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>0.21</v>
+        <v>0.08</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>0.21</v>
+        <v>0.08</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.21</v>
+        <v>0.08</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.21</v>
+        <v>0.08</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.21</v>
+        <v>0.08</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>0.21</v>
+        <v>0.08</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>0.21</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="26">
@@ -2242,28 +2348,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.395</v>
+        <v>0.428</v>
       </c>
       <c r="C26" t="n">
-        <v>0.471</v>
+        <v>0.546</v>
       </c>
       <c r="D26" t="n">
-        <v>0.55</v>
+        <v>0.617</v>
       </c>
       <c r="E26" t="n">
-        <v>0.63</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>0.704</v>
+        <v>0.756</v>
       </c>
       <c r="G26" t="n">
-        <v>0.771</v>
+        <v>0.802</v>
       </c>
       <c r="H26" t="n">
-        <v>0.831</v>
+        <v>0.842</v>
       </c>
       <c r="I26" t="n">
-        <v>0.885</v>
+        <v>0.876</v>
       </c>
     </row>
     <row r="27">
@@ -2273,28 +2379,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.08</v>
+        <v>0.093</v>
       </c>
       <c r="C27" t="n">
-        <v>0.093</v>
+        <v>0.099</v>
       </c>
       <c r="D27" t="n">
-        <v>0.106</v>
+        <v>0.11</v>
       </c>
       <c r="E27" t="n">
-        <v>0.119</v>
+        <v>0.12</v>
       </c>
       <c r="F27" t="n">
-        <v>0.131</v>
+        <v>0.129</v>
       </c>
       <c r="G27" t="n">
-        <v>0.141</v>
+        <v>0.136</v>
       </c>
       <c r="H27" t="n">
-        <v>0.151</v>
+        <v>0.143</v>
       </c>
       <c r="I27" t="n">
-        <v>0.16</v>
+        <v>0.149</v>
       </c>
     </row>
     <row r="28">
@@ -2304,28 +2410,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.08</v>
+        <v>0.242</v>
       </c>
       <c r="C28" t="n">
-        <v>0.093</v>
+        <v>0.138</v>
       </c>
       <c r="D28" t="n">
-        <v>0.096</v>
+        <v>0.122</v>
       </c>
       <c r="E28" t="n">
-        <v>0.107</v>
+        <v>0.12</v>
       </c>
       <c r="F28" t="n">
-        <v>0.105</v>
+        <v>0.129</v>
       </c>
       <c r="G28" t="n">
-        <v>0.113</v>
+        <v>0.136</v>
       </c>
       <c r="H28" t="n">
-        <v>0.114</v>
+        <v>0.143</v>
       </c>
       <c r="I28" t="n">
-        <v>0.12</v>
+        <v>0.149</v>
       </c>
     </row>
     <row r="29">
@@ -2335,28 +2441,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.08</v>
+        <v>0.047</v>
       </c>
       <c r="C29" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.044</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.037</v>
       </c>
       <c r="E29" t="n">
-        <v>0.083</v>
+        <v>0.033</v>
       </c>
       <c r="F29" t="n">
-        <v>0.079</v>
+        <v>0.029</v>
       </c>
       <c r="G29" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.023</v>
       </c>
       <c r="H29" t="n">
-        <v>0.076</v>
+        <v>0.024</v>
       </c>
       <c r="I29" t="n">
-        <v>0.064</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="30">
@@ -2366,25 +2472,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.315</v>
+        <v>0.233</v>
       </c>
       <c r="C30" t="n">
-        <v>0.387</v>
+        <v>0.462</v>
       </c>
       <c r="D30" t="n">
-        <v>0.475</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.652</v>
       </c>
       <c r="F30" t="n">
-        <v>0.651</v>
+        <v>0.729</v>
       </c>
       <c r="G30" t="n">
-        <v>0.728</v>
+        <v>0.781</v>
       </c>
       <c r="H30" t="n">
-        <v>0.793</v>
+        <v>0.82</v>
       </c>
       <c r="I30" t="n">
         <v>0.861</v>
@@ -2397,28 +2503,28 @@
         </is>
       </c>
       <c r="B31" s="15" t="n">
-        <v>0.9025</v>
+        <v>0.905</v>
       </c>
       <c r="C31" s="15" t="n">
-        <v>0.8146</v>
+        <v>0.819</v>
       </c>
       <c r="D31" s="15" t="n">
-        <v>0.7352</v>
+        <v>0.7412</v>
       </c>
       <c r="E31" s="15" t="n">
-        <v>0.6635</v>
+        <v>0.6707</v>
       </c>
       <c r="F31" s="15" t="n">
-        <v>0.5988</v>
+        <v>0.607</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>0.5405</v>
+        <v>0.5493</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>0.4878</v>
+        <v>0.4971</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>0.4402</v>
+        <v>0.4499</v>
       </c>
     </row>
     <row r="32">
@@ -2428,28 +2534,28 @@
         </is>
       </c>
       <c r="B32" s="16" t="n">
-        <v>0.284</v>
+        <v>0.211</v>
       </c>
       <c r="C32" s="16" t="n">
-        <v>0.315</v>
+        <v>0.378</v>
       </c>
       <c r="D32" s="16" t="n">
-        <v>0.349</v>
+        <v>0.42</v>
       </c>
       <c r="E32" s="16" t="n">
-        <v>0.37</v>
+        <v>0.437</v>
       </c>
       <c r="F32" s="16" t="n">
-        <v>0.39</v>
+        <v>0.443</v>
       </c>
       <c r="G32" s="16" t="n">
-        <v>0.393</v>
+        <v>0.429</v>
       </c>
       <c r="H32" s="16" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="I32" s="16" t="n">
         <v>0.387</v>
-      </c>
-      <c r="I32" s="16" t="n">
-        <v>0.379</v>
       </c>
     </row>
     <row r="33"/>
@@ -2487,7 +2593,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>11.36961538461538</v>
+        <v>11.8244</v>
       </c>
     </row>
     <row r="38">
@@ -2497,7 +2603,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5.005272082257082</v>
+        <v>5.319623410644886</v>
       </c>
     </row>
     <row r="39"/>
@@ -2508,7 +2614,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.868</v>
+        <v>3.113</v>
       </c>
     </row>
     <row r="41">
@@ -2518,7 +2624,7 @@
         </is>
       </c>
       <c r="B41" s="16" t="n">
-        <v>7.873</v>
+        <v>8.433</v>
       </c>
     </row>
     <row r="42">
@@ -2528,7 +2634,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.9</v>
+        <v>-0.9409999999999999</v>
       </c>
     </row>
     <row r="43">
@@ -2538,7 +2644,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>8.773</v>
+        <v>9.374000000000001</v>
       </c>
     </row>
     <row r="44">
@@ -2559,7 +2665,7 @@
         </is>
       </c>
       <c r="B46" s="19" t="n">
-        <v>244.86</v>
+        <v>261.62</v>
       </c>
     </row>
   </sheetData>
@@ -2643,12 +2749,12 @@
       </c>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t>0.0430 + 1.300 x 0.0500</t>
+          <t>0.0450 + 1.300 x 0.0460</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>0.1080 (10.80%)</t>
+          <t>0.1048 (10.48%)</t>
         </is>
       </c>
     </row>
@@ -2660,12 +2766,12 @@
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>1.00 x 0.1080</t>
+          <t>1.00 x 0.1048</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>0.1080</t>
+          <t>0.1046</t>
         </is>
       </c>
     </row>
@@ -2677,12 +2783,12 @@
       </c>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t>0.00 x 0.0000</t>
+          <t>0.00 x 0.0300</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0001</t>
         </is>
       </c>
     </row>
@@ -2694,12 +2800,12 @@
       </c>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t>0.1080 + 0.0000</t>
+          <t>0.1046 + 0.0001</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>0.1080 (10.80%)</t>
+          <t>0.1050 (10.50%)</t>
         </is>
       </c>
     </row>
@@ -2762,13 +2868,13 @@
         <v>2026</v>
       </c>
       <c r="B16" t="n">
-        <v>0.315</v>
+        <v>0.233</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9025</v>
+        <v>0.905</v>
       </c>
       <c r="D16" t="n">
-        <v>0.284</v>
+        <v>0.211</v>
       </c>
     </row>
     <row r="17">
@@ -2776,13 +2882,13 @@
         <v>2027</v>
       </c>
       <c r="B17" t="n">
-        <v>0.387</v>
+        <v>0.462</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8146</v>
+        <v>0.819</v>
       </c>
       <c r="D17" t="n">
-        <v>0.315</v>
+        <v>0.378</v>
       </c>
     </row>
     <row r="18">
@@ -2790,13 +2896,13 @@
         <v>2028</v>
       </c>
       <c r="B18" t="n">
-        <v>0.475</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7352</v>
+        <v>0.7412</v>
       </c>
       <c r="D18" t="n">
-        <v>0.349</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="19">
@@ -2804,13 +2910,13 @@
         <v>2029</v>
       </c>
       <c r="B19" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.652</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6635</v>
+        <v>0.6707</v>
       </c>
       <c r="D19" t="n">
-        <v>0.37</v>
+        <v>0.437</v>
       </c>
     </row>
     <row r="20">
@@ -2818,13 +2924,13 @@
         <v>2030</v>
       </c>
       <c r="B20" t="n">
-        <v>0.651</v>
+        <v>0.729</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5988</v>
+        <v>0.607</v>
       </c>
       <c r="D20" t="n">
-        <v>0.39</v>
+        <v>0.443</v>
       </c>
     </row>
     <row r="21">
@@ -2832,13 +2938,13 @@
         <v>2031</v>
       </c>
       <c r="B21" t="n">
-        <v>0.728</v>
+        <v>0.781</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5405</v>
+        <v>0.5493</v>
       </c>
       <c r="D21" t="n">
-        <v>0.393</v>
+        <v>0.429</v>
       </c>
     </row>
     <row r="22">
@@ -2846,13 +2952,13 @@
         <v>2032</v>
       </c>
       <c r="B22" t="n">
-        <v>0.793</v>
+        <v>0.82</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4878</v>
+        <v>0.4971</v>
       </c>
       <c r="D22" t="n">
-        <v>0.387</v>
+        <v>0.408</v>
       </c>
     </row>
     <row r="23">
@@ -2863,10 +2969,10 @@
         <v>0.861</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4402</v>
+        <v>0.4499</v>
       </c>
       <c r="D23" t="n">
-        <v>0.379</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="24">
@@ -2877,7 +2983,7 @@
       </c>
       <c r="D24" s="22" t="inlineStr">
         <is>
-          <t>2.868B</t>
+          <t>3.113B</t>
         </is>
       </c>
     </row>
@@ -2955,12 +3061,12 @@
       </c>
       <c r="B31" s="21" t="inlineStr">
         <is>
-          <t>0.887 / (0.1080 - 0.0300)</t>
+          <t>0.887 / (0.1050 - 0.0300)</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>11.370B</t>
+          <t>11.824B</t>
         </is>
       </c>
     </row>
@@ -2972,12 +3078,12 @@
       </c>
       <c r="B32" s="21" t="inlineStr">
         <is>
-          <t>11.370 / (1+0.1080)^8</t>
+          <t>11.824 / (1+0.1050)^8</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>5.005B</t>
+          <t>5.320B</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3127,12 @@
       </c>
       <c r="B37" s="21" t="inlineStr">
         <is>
-          <t>2.868 + 5.005</t>
+          <t>3.113 + 5.320</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>7.873B</t>
+          <t>8.433B</t>
         </is>
       </c>
     </row>
@@ -3038,12 +3144,12 @@
       </c>
       <c r="B38" s="21" t="inlineStr">
         <is>
-          <t>7.873 - -0.900</t>
+          <t>8.433 - -0.941</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>8.773B</t>
+          <t>9.374B</t>
         </is>
       </c>
     </row>
@@ -3055,12 +3161,12 @@
       </c>
       <c r="B39" s="21" t="inlineStr">
         <is>
-          <t>8.773B / 0.036B shares</t>
+          <t>9.374B / 0.036B shares</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>$244.86</t>
+          <t>$261.62</t>
         </is>
       </c>
     </row>
@@ -3139,111 +3245,111 @@
     <row r="4">
       <c r="A4" s="20" t="inlineStr">
         <is>
-          <t>9.80%</t>
+          <t>9.50%</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>257.42</v>
+        <v>275.1</v>
       </c>
       <c r="C4" t="n">
-        <v>268.38</v>
+        <v>287.23</v>
       </c>
       <c r="D4" t="n">
-        <v>280.96</v>
+        <v>301.22</v>
       </c>
       <c r="E4" t="n">
-        <v>295.54</v>
+        <v>317.54</v>
       </c>
       <c r="F4" t="n">
-        <v>312.63</v>
+        <v>336.83</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="inlineStr">
         <is>
-          <t>10.30%</t>
+          <t>10.00%</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>241.69</v>
+        <v>257.97</v>
       </c>
       <c r="C5" t="n">
-        <v>251.03</v>
+        <v>268.25</v>
       </c>
       <c r="D5" t="n">
-        <v>261.65</v>
+        <v>279.99</v>
       </c>
       <c r="E5" t="n">
-        <v>273.84</v>
+        <v>293.54</v>
       </c>
       <c r="F5" t="n">
-        <v>287.96</v>
+        <v>309.35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>10.80%</t>
+          <t>10.50%</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>227.78</v>
+        <v>242.88</v>
       </c>
       <c r="C6" t="n">
-        <v>235.81</v>
+        <v>251.67</v>
       </c>
       <c r="D6" t="n">
-        <v>244.86</v>
+        <v>261.62</v>
       </c>
       <c r="E6" t="n">
-        <v>255.15</v>
+        <v>273</v>
       </c>
       <c r="F6" t="n">
-        <v>266.96</v>
+        <v>286.13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="inlineStr">
         <is>
-          <t>11.30%</t>
+          <t>11.00%</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>215.41</v>
+        <v>229.5</v>
       </c>
       <c r="C7" t="n">
-        <v>222.35</v>
+        <v>237.06</v>
       </c>
       <c r="D7" t="n">
-        <v>230.13</v>
+        <v>245.57</v>
       </c>
       <c r="E7" t="n">
-        <v>238.9</v>
+        <v>255.22</v>
       </c>
       <c r="F7" t="n">
-        <v>248.87</v>
+        <v>266.24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>11.80%</t>
+          <t>11.50%</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>204.34</v>
+        <v>217.55</v>
       </c>
       <c r="C8" t="n">
-        <v>210.38</v>
+        <v>224.11</v>
       </c>
       <c r="D8" t="n">
-        <v>217.1</v>
+        <v>231.44</v>
       </c>
       <c r="E8" t="n">
-        <v>224.64</v>
+        <v>239.69</v>
       </c>
       <c r="F8" t="n">
-        <v>233.14</v>
+        <v>249.03</v>
       </c>
     </row>
   </sheetData>
@@ -3263,7 +3369,7 @@
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="80" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="80" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -3323,19 +3429,19 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>30</v>
+        <v>34.1</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="D5" s="23" t="n">
-        <v>0.18</v>
+        <v>0.356</v>
       </c>
       <c r="E5" s="23" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="F5" s="23" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="6">
@@ -3345,19 +3451,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>48</v>
+        <v>47.1</v>
       </c>
       <c r="C6" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>0.24</v>
+        <v>0.205</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>3.6</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="7">
@@ -3367,19 +3473,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="C7" t="n">
-        <v>22</v>
+        <v>124</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>0.18</v>
+        <v>0.9009999999999999</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>1.1</v>
+        <v>9.07</v>
       </c>
     </row>
     <row r="8">
@@ -3389,19 +3495,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>18.8</v>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>0.08</v>
+        <v>1.023</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>0.7</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="9">
@@ -3411,41 +3517,41 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>20.6</v>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>27.1</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>0.05</v>
+        <v>0.169</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.55</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>AAOI</t>
+          <t>CLS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>40</v>
+        <v>25.5</v>
       </c>
       <c r="C10" t="n">
-        <v>35</v>
+        <v>32.2</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>0.3</v>
+        <v>0.528</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="11"/>
@@ -3457,7 +3563,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Fabrinet sits awkwardly between two cohorts. Against optical-component makers Coherent and Lumentum it grows similarly but owns less IP, yet it trades at a comparable or higher multiple. Against its true economic peers, contract manufacturers Sanmina and Flex at 9-11x EV/EBITDA, it trades at more than double on growth that is faster but built on the same thin-margin assembly model. The market is pricing Fabrinet as an optical-technology play; its income statement says contract manufacturer. That gap between perceived and actual business model is the core of the valuation risk.</t>
+          <t>The peer set is uniformly expensive. Coherent at 58x EBITDA and Lumentum at 124x are pricing in optical-IP-company economics that Fabrinet's contract-assembly model doesn't share. Sanmina's 19x and Flex's 27x are the true EMS comps, and FN at 42x EBITDA sits 50-100% above them. Celestica at 32x is the closest structural analog: a complex-EMS company with significant AI infrastructure exposure. At 34x forward P/E, Fabrinet is cheaper than COHR and LITE on that metric, which bears watching. But the core issue is not how Fabrinet ranks within an expensive sector -- it's that the entire optical-AI EMS sector is pricing in sustained 30-50% growth indefinitely, and Fabrinet's contract-manufacturer economics cap the upside in any return-to-normalcy scenario.</t>
         </is>
       </c>
     </row>
@@ -3508,14 +3614,14 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>267.93</v>
+        <v>337.73</v>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>EV/EBITDA cross-check against optical-component and contract-manufacturing peers. Even a generous multiple for an asset-light optical assembler lands below the post-run share price.</t>
+          <t>EV/EBITDA cross-check blending optical-component peers (COHR ~35-40x, LITE ~22x) with EMS peers (SANM ~9x, FLEX ~9x, CLS ~15x). Fabrinet earns a premium over generic EMS for optical complexity and secular growth, but trades at a discount to optical-IP companies. A blended cross-check multiple of 20x applied to FY2026E EBITDA is defensible at the midpoint.</t>
         </is>
       </c>
     </row>
@@ -3600,22 +3706,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>144.31</v>
+        <v>149.29</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="D5" t="n">
-        <v>36.08</v>
+        <v>29.86</v>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>A full quarter-weight. FN is customer-concentrated (a few large transceiver/networking OEMs), margins are thin, and the shares have ~2.5x'd off the low. A single program shift or a move to in-house/CPO assembly hurts.</t>
+          <t>20% weight. This scenario requires either a structural demand event (CPO displacing pluggable module volumes, a key customer in-sourcing or dual-sourcing, or AI-optical capex correction) or multiple compression toward EMS-peer norms without a fundamental trigger. The company's track record of execution and its strong Q3 FY2026 results lower the probability relative to a company with weaker fundamentals, but the valuation leaves no margin for error. Customer concentration and negative TTM FCF are the two most credible near-term catalysts for this scenario.</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>Optical-module volumes digest, a key customer in-sources or shifts to co-packaged optics, and the multiple compresses.</t>
+          <t>Hyperscaler capex digestion cuts Datacom and DCI growth; customer concentration event or CPO architectural shift compresses the multiple from 42x to 15-20x EBITDA.</t>
         </is>
       </c>
     </row>
@@ -3626,22 +3732,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>244.86</v>
+        <v>261.62</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="D6" t="n">
-        <v>110.19</v>
+        <v>130.81</v>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Central case. FN keeps winning AI optical assembly and margins inch up, but the valuation already prices a long, smooth datacom ramp.</t>
+          <t>50% weight. Central case assumes Fabrinet continues to win optical assembly programs as modeled, supply constraints ease in H2 calendar 2026, and Building 10 fills over two to three years. Revenue growth decelerates from 35% to 18% to 10% across the explicit period. Operating margin improves gradually from 10% to 11.5%. The question is not whether the business is good -- it is -- but whether $587 reflects even the central case. The DCF at 10.5% WACC says it does not.</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Datacom-led growth decelerating from 18% to mid-single-digits, operating margin grinding from 12.5% to ~14%.</t>
+          <t>Supply constraints ease, new Datacom programs ramp in FY2027, HPC stabilizes at $150M+ quarterly; revenue growth decelerates from 35% to 10% range, margins tick to 11.5%.</t>
         </is>
       </c>
     </row>
@@ -3652,22 +3758,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>338.32</v>
+        <v>472.91</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="D7" t="n">
-        <v>33.83</v>
+        <v>70.94</v>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>Lower odds. Requires 1.6T and co-packaged-optics assembly to flow to FN at scale and margins to expand above plan.</t>
+          <t>15% weight. Bull case requires: (1) supply constraints release explosively, taking Datacom to $350M+ per quarter; (2) CPO/OCS program wins with named customers materialize in FY2027-2028; (3) Building 10 fills faster than modeled, driving operating leverage above 12%; (4) terminal growth at 4% implies Fabrinet successfully captures CPO assembly revenue that offsets any pluggable-module attrition. A credible scenario given the depth of the opportunity pipeline, but requires execution across multiple fronts simultaneously.</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>Fabrinet becomes the default high-complexity optical-engine assembler; revenue and margins beat the base path.</t>
+          <t>Supply constraint release plus CPO/OCS program wins push revenue toward $6B+ by FY2028; FCF margin expands to 10%+ on operating leverage; terminal growth rate reflects sustained optical-assembly leadership.</t>
         </is>
       </c>
     </row>
@@ -3678,17 +3784,17 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>267.93</v>
+        <v>337.73</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="D8" t="n">
-        <v>53.59</v>
+        <v>50.66</v>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>EV/EBITDA cross-check against optical-component and contract-manufacturing peers. Even a generous multiple for an asset-light optical assembler lands below the post-run share price.</t>
+          <t>EV/EBITDA cross-check blending optical-component peers (COHR ~35-40x, LITE ~22x) with EMS peers (SANM ~9x, FLEX ~9x, CLS ~15x). Fabrinet earns a premium over generic EMS for optical complexity and secular growth, but trades at a discount to optical-IP companies. A blended cross-check multiple of 20x applied to FY2026E EBITDA is defensible at the midpoint.</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -3715,7 +3821,7 @@
         </is>
       </c>
       <c r="D11" s="19" t="n">
-        <v>233.69</v>
+        <v>282.27</v>
       </c>
     </row>
     <row r="12">
@@ -3725,7 +3831,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>586</v>
+        <v>587.41</v>
       </c>
     </row>
     <row r="13">
@@ -3735,7 +3841,7 @@
         </is>
       </c>
       <c r="D13" s="25" t="n">
-        <v>-0.601</v>
+        <v>-0.519</v>
       </c>
     </row>
     <row r="14"/>
@@ -3750,7 +3856,7 @@
     <row r="17" ht="60" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Bear 25% because customer concentration, thin margins and a ~2.5x run leave little room for error, and co-packaged optics is a structural overhang. Base 45% for the continued AI optical ramp. Bull 10% for a CPO/1.6T assembly win. Cross-check 20% anchors against optical/manufacturing multiples.</t>
+          <t>Base 50% is the anchor: modeled revenue growth and margin expansion are realistic given actual Q3 FY2026 results, but the DCF says fair value is well below spot. Bear 20% acknowledges the real risk that Datacom demand is inventory-cycle driven rather than structural, and that any customer concentration event can step revenues down sharply. Bull 15% reflects the genuine optionality in CPO/OCS/hyperscale Datacom wins that are being actively qualified. Cross-check 15% adds a relative discipline: even at a generous 20x EBITDA versus EMS peers at 9-15x, the stock is rich. Probabilities sum with cross-check: 0.20 + 0.50 + 0.15 + 0.15 = 1.00.</t>
         </is>
       </c>
     </row>
